--- a/1.0excel/class/304_3_5_VH_LOOKUP_index_match.xlsx
+++ b/1.0excel/class/304_3_5_VH_LOOKUP_index_match.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\ds_materials\1.0excel\class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADD0A18-8D01-48D5-87B6-884B8C63B604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1922621D-5C5B-471A-A8DE-C22F52DE0C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
     <sheet name="index-match" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="93">
   <si>
     <t>Below is a list of the employees who work in your company:</t>
   </si>
@@ -341,17 +364,30 @@
   <si>
     <t>take a value and return index number</t>
   </si>
+  <si>
+    <t>based on the locations find the emp name , and  salary using index match</t>
+  </si>
+  <si>
+    <t>usa</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -522,38 +558,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -858,11 +898,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" customWidth="1"/>
     <col min="9" max="9" width="9.42578125" customWidth="1"/>
@@ -870,12 +912,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:11">
@@ -884,10 +926,10 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>49</v>
       </c>
     </row>
@@ -913,7 +955,7 @@
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="21" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1003,13 +1045,13 @@
       <c r="E7" s="13">
         <v>32</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="20" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1057,7 +1099,7 @@
       <c r="E9" s="13">
         <v>35</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="20" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1077,7 +1119,7 @@
       <c r="E10" s="13">
         <v>25</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="20" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1208,6 +1250,36 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" ht="51.75" customHeight="1">
+      <c r="B21" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="B22" s="22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="B23">
+        <f>MATCH(B22,C4:C15,0)</f>
+        <v>7</v>
+      </c>
+      <c r="C23" t="str" cm="1">
+        <f t="array" ref="C23">INDEX(B4:B15,B23)</f>
+        <v>Paul Bell</v>
+      </c>
+      <c r="D23">
+        <f>INDEX(D4:D15,MATCH(B22,C4:C15,0))</f>
+        <v>10387</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2135,10 +2207,10 @@
       <c r="B2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2147,10 +2219,10 @@
       <c r="B3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="20" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2187,7 +2259,7 @@
       <c r="B8" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>70</v>
       </c>
       <c r="F8">
